--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92994858999</v>
+        <v>46157.9308349529</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9308349529</v>
+        <v>46157.93353019635</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93353019635</v>
+        <v>46157.93642502119</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93642502119</v>
+        <v>46158.28178281408</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28178281408</v>
+        <v>46158.29754542551</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92967680548</v>
+        <v>46158.29721491433</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         <v>0.01</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>46157.92967680548</v>
+        <v>46158.29721491433</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>46157.92967680548</v>
+        <v>46158.29721491433</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29754542551</v>
+        <v>46158.29773008418</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29773008418</v>
+        <v>46158.30446648056</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.30446648056</v>
+        <v>46158.33341653556</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33341653556</v>
+        <v>46158.37202221868</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/08_Аренда/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37202221868</v>
+        <v>46158.37418653889</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,7 +721,7 @@
         <v>6.4</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46158.29721491433</v>
+        <v>46158.37378163124</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         <v>0.01</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>46158.29721491433</v>
+        <v>46158.37378163124</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>46158.29721491433</v>
+        <v>46158.37378163124</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
